--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487634_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487634_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.338800000000001</v>
+        <v>7.0796</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4705</v>
+        <v>6.2112</v>
       </c>
       <c r="F2" t="n">
         <v>0.8683</v>
@@ -610,10 +610,10 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7351</v>
+        <v>0.4758</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1366</v>
+        <v>0.8773</v>
       </c>
       <c r="U2" t="n">
         <v>-0.4015</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0111</v>
+        <v>0.7892</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1462</v>
+        <v>0.7063</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1352</v>
+        <v>0.0829</v>
       </c>
       <c r="G3" t="n">
         <v>-3.4125</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3022</v>
+        <v>-0.5241</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5596</v>
+        <v>0.1197</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8618</v>
+        <v>-0.6438</v>
       </c>
       <c r="V3" t="n">
         <v>3.1734</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2327</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4588</v>
+        <v>1.0603</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2261</v>
+        <v>-1.142</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.143</v>
+        <v>0.287</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8733</v>
+        <v>2.1783</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.0164</v>
+        <v>-1.8913</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7966</v>
+        <v>2.3366</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1668</v>
+        <v>3.6662</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3702</v>
+        <v>-1.3296</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9397</v>
+        <v>-2.0496</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2935</v>
+        <v>-1.4879</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6462</v>
+        <v>-0.5617</v>
       </c>
       <c r="P4" t="n">
         <v>-0.194</v>
@@ -766,28 +766,28 @@
         <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7158</v>
+        <v>-1.1824</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5607</v>
+        <v>-0.2016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.155</v>
+        <v>-0.9808</v>
       </c>
       <c r="V4" t="n">
-        <v>1.854</v>
+        <v>1.0078</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0119</v>
+        <v>1.8358</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1579</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. PEÑA LOPEZ</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6725</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0606</v>
+        <v>0.9398</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6119</v>
+        <v>-1.6076</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6119</v>
+        <v>-2.143</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.206</v>
+        <v>0.8733</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.406</v>
+        <v>-3.0164</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.7966</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.1668</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.3702</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6119</v>
+        <v>-2.9397</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.206</v>
+        <v>-1.2935</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.406</v>
+        <v>-1.6462</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7164</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0606</v>
+        <v>-0.1848</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0606</v>
+        <v>0.0417</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.2265</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.854</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.0119</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1579</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>F. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9547</v>
+        <v>-0.6725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3781</v>
+        <v>-0.0606</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3328</v>
+        <v>-0.6119</v>
       </c>
       <c r="G6" t="n">
-        <v>0.287</v>
+        <v>-0.6119</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1783</v>
+        <v>-0.206</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8913</v>
+        <v>-0.406</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3366</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6662</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3296</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0496</v>
+        <v>-0.6119</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4879</v>
+        <v>-0.206</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5617</v>
+        <v>-0.406</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7164</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0554</v>
+        <v>-0.0606</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8838</v>
+        <v>-0.0606</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1716</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0078</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0314</v>
+        <v>-1.4314</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3036</v>
+        <v>-0.9217</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7278</v>
+        <v>-0.5098</v>
       </c>
       <c r="G7" t="n">
         <v>1.2388</v>
@@ -1000,13 +1000,13 @@
         <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7642</v>
+        <v>-0.1643</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1694</v>
+        <v>0.2125</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5949</v>
+        <v>-0.3768</v>
       </c>
       <c r="V7" t="n">
         <v>-2.1179</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7722</v>
+        <v>-1.727</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.289</v>
+        <v>-1.6461</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4832</v>
+        <v>-0.0809</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8869</v>
+        <v>-2.3183</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1295</v>
+        <v>-0.9203</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7573</v>
+        <v>-1.3981</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9072</v>
+        <v>-0.8141</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2399</v>
+        <v>-0.1112</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6673</v>
+        <v>-0.7029</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9796</v>
+        <v>-1.5042</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1104</v>
+        <v>-0.8091</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.09</v>
+        <v>-0.6952</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2734</v>
+        <v>-0.7669</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6057</v>
+        <v>0.1382</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3322</v>
+        <v>-0.9051</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0943</v>
+        <v>-2.3959</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8498</v>
+        <v>-0.6674</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2445</v>
+        <v>-1.7285</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3183</v>
+        <v>-2.8869</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9203</v>
+        <v>-1.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3981</v>
+        <v>-1.7573</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8141</v>
+        <v>-1.9072</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1112</v>
+        <v>-1.2399</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7029</v>
+        <v>-0.6673</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5042</v>
+        <v>-0.9796</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8091</v>
+        <v>0.1104</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6952</v>
+        <v>-1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3284</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1341</v>
+        <v>0.1029</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0655</v>
+        <v>0.016</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0686</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3694</v>
+        <v>-3.1058</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6137</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.883</v>
+        <v>-3.7195</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2539</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3457</v>
+        <v>-1.082</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8479</v>
+        <v>-0.7478</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4977</v>
+        <v>-0.3342</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1579</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3354</v>
+        <v>-4.6928</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5528</v>
+        <v>-2.9101</v>
       </c>
       <c r="F11" t="n">
         <v>-1.7827</v>
@@ -1312,10 +1312,10 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4969</v>
+        <v>0.1458</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2075</v>
+        <v>0.8501</v>
       </c>
       <c r="U11" t="n">
         <v>-0.7043</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4046</v>
+        <v>-6.6315</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6728</v>
+        <v>-4.5727</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7318</v>
+        <v>-2.0589</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2036</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4132</v>
+        <v>-0.6401</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6057</v>
+        <v>-0.5056</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1925</v>
+        <v>-0.1346</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8176</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.0519</v>
+        <v>-13.5376</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.761399999999999</v>
+        <v>-1.2473</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.2907</v>
+        <v>-12.2906</v>
       </c>
       <c r="G13" t="n">
         <v>-13.1511</v>
@@ -1468,10 +1468,10 @@
         <v>15.5227</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3948</v>
+        <v>-3.8807</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7741999999999998</v>
+        <v>0.7398999999999998</v>
       </c>
       <c r="U13" t="n">
         <v>-4.6207</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.627000000000001</v>
+        <v>10.331</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2886</v>
+        <v>8.2896</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3384</v>
+        <v>2.0414</v>
       </c>
       <c r="G14" t="n">
         <v>9.5184</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0675</v>
+        <v>0.6365</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.775</v>
+        <v>0.226</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2925</v>
+        <v>0.4105</v>
       </c>
       <c r="V14" t="n">
         <v>0.5642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4881</v>
+        <v>6.5754</v>
       </c>
       <c r="E15" t="n">
-        <v>8.3569</v>
+        <v>7.5561</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8688</v>
+        <v>-0.9807</v>
       </c>
       <c r="G15" t="n">
         <v>4.7121</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2983</v>
+        <v>1.3857</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5298</v>
+        <v>0.729</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7685</v>
+        <v>0.6567</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6866</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.286</v>
+        <v>3.9256</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0695</v>
+        <v>2.7692</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2165</v>
+        <v>1.1564</v>
       </c>
       <c r="G16" t="n">
         <v>2.212</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2427</v>
+        <v>1.8823</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6633</v>
+        <v>1.363</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5795</v>
+        <v>0.5193</v>
       </c>
       <c r="V16" t="n">
         <v>1.3836</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2976</v>
+        <v>1.2806</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7342</v>
+        <v>1.2472</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0317</v>
+        <v>0.0334</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1725</v>
+        <v>0.8143</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6344</v>
+        <v>-0.1434</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8069</v>
+        <v>0.9576</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.9616</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3707</v>
+        <v>0.7992</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2842</v>
+        <v>0.1624</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2591</v>
+        <v>-0.1473</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2637</v>
+        <v>-0.9425</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.7952</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3284</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3638</v>
+        <v>0.2305</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6808</v>
+        <v>0.226</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6831</v>
+        <v>0.0045</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5373</v>
+        <v>-0.7343</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5373</v>
+        <v>-1.9582</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8078</v>
+        <v>1.1324</v>
       </c>
       <c r="E18" t="n">
-        <v>1.047</v>
+        <v>0.9072</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2392</v>
+        <v>0.2252</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8143</v>
+        <v>0.2321</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1434</v>
+        <v>-0.1038</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9576</v>
+        <v>0.3359</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9616</v>
+        <v>0.6552</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7992</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1624</v>
+        <v>0.614</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1473</v>
+        <v>-0.4231</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9425</v>
+        <v>-0.145</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7952</v>
+        <v>-0.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2423</v>
+        <v>0.1242</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0258</v>
+        <v>0.2521</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.268</v>
+        <v>-0.1278</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7343</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7532</v>
+        <v>1.0946</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6069</v>
+        <v>-1.9343</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1462</v>
+        <v>3.0289</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2321</v>
+        <v>0.1725</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1038</v>
+        <v>-0.6344</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3359</v>
+        <v>0.8069</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6552</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0412</v>
+        <v>-0.3707</v>
       </c>
       <c r="L19" t="n">
-        <v>0.614</v>
+        <v>0.2842</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4231</v>
+        <v>0.2591</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.145</v>
+        <v>-0.2637</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2781</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3284</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.255</v>
+        <v>1.1608</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0482</v>
+        <v>0.4806</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2068</v>
+        <v>0.6803</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5373</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.5373</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3838</v>
+        <v>0.1925</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.281</v>
+        <v>-0.5813</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.7738</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0136</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0973</v>
+        <v>-0.0939</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4374</v>
+        <v>0.1371</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3401</v>
+        <v>-0.231</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8538</v>
+        <v>-0.6073</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5457</v>
+        <v>-1.2142</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.308</v>
+        <v>0.6069</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0883</v>
+        <v>-0.3897</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7285</v>
+        <v>-0.4531</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3598</v>
+        <v>0.0634</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2529</v>
+        <v>-0.538</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6261</v>
+        <v>0.0659</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6267</v>
+        <v>-0.6039</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8354</v>
+        <v>0.1483</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1023</v>
+        <v>-0.5191</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2669</v>
+        <v>0.6673</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5821</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3703</v>
+        <v>-0.1668</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4251</v>
+        <v>0.0283</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0547</v>
+        <v>-0.1951</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2821</v>
+        <v>2.2776</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2169</v>
+        <v>-1.0267</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7147</v>
+        <v>-0.7459</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4979</v>
+        <v>-0.2808</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3897</v>
+        <v>-2.0883</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4531</v>
+        <v>-1.7285</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0634</v>
+        <v>-0.3598</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.538</v>
+        <v>-1.2529</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0659</v>
+        <v>-0.6261</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6039</v>
+        <v>-0.6267</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1483</v>
+        <v>-0.8354</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5191</v>
+        <v>-1.1023</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6673</v>
+        <v>0.2669</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3284</v>
+        <v>0.5821</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7763</v>
+        <v>0.1974</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4722</v>
+        <v>0.2249</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3042</v>
+        <v>-0.0275</v>
       </c>
       <c r="V22" t="n">
-        <v>2.2776</v>
+        <v>0.2821</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4</v>
+        <v>0.2821</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7458</v>
+        <v>-1.0601</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3903</v>
+        <v>-1.8898</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6445</v>
+        <v>0.8297</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6112</v>
@@ -2248,13 +2248,13 @@
         <v>1.3582</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3584</v>
+        <v>0.3272</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3634</v>
+        <v>0.1371</v>
       </c>
       <c r="U23" t="n">
-        <v>0.005</v>
+        <v>0.1901</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2841</v>
+        <v>-2.4932</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9889</v>
+        <v>-1.089</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2952</v>
+        <v>-1.4042</v>
       </c>
       <c r="G24" t="n">
         <v>0.0064</v>
@@ -2326,13 +2326,13 @@
         <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7393</v>
+        <v>0.5302</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4856</v>
+        <v>0.3855</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2537</v>
+        <v>0.1447</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4477</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4911</v>
+        <v>-2.9582</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4236</v>
+        <v>-1.0242</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0675</v>
+        <v>-1.934</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4139</v>
@@ -2404,13 +2404,13 @@
         <v>1.3582</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9825</v>
+        <v>0.5154</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0318</v>
+        <v>0.4312</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0493</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4477</v>
@@ -2437,25 +2437,25 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>15.05180000000001</v>
+        <v>16.3866</v>
       </c>
       <c r="E26" t="n">
-        <v>12.2905</v>
+        <v>12.2906</v>
       </c>
       <c r="F26" t="n">
-        <v>2.761299999999999</v>
+        <v>4.095999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>13.1511</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9721000000000011</v>
+        <v>0.9721000000000006</v>
       </c>
       <c r="I26" t="n">
         <v>12.179</v>
       </c>
       <c r="J26" t="n">
-        <v>15.1465</v>
+        <v>15.14649999999999</v>
       </c>
       <c r="K26" t="n">
         <v>6.887700000000001</v>
@@ -2482,19 +2482,19 @@
         <v>13.5822</v>
       </c>
       <c r="S26" t="n">
-        <v>5.394699999999999</v>
+        <v>6.7295</v>
       </c>
       <c r="T26" t="n">
-        <v>4.6208</v>
+        <v>4.620800000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7741999999999999</v>
+        <v>2.108799999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5536</v>
       </c>
       <c r="W26" t="n">
-        <v>8.0463</v>
+        <v>8.046299999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-9.5999</v>
